--- a/Mod_Korean/Lang/KR/Game/Zone.xlsx
+++ b/Mod_Korean/Lang/KR/Game/Zone.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="740" uniqueCount="549">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="742" uniqueCount="551">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -53,7 +53,7 @@
     <t xml:space="preserve">world</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.237 Patch 1</t>
+    <t xml:space="preserve">EA 23.247</t>
   </si>
   <si>
     <t xml:space="preserve">Ylva</t>
@@ -720,6 +720,12 @@
   </si>
   <si>
     <t xml:space="preserve">死者の洞窟</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A cold shiver ran through you, freezing you from the inside out.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">体の芯まで凍りつくような寒気を感じる。</t>
   </si>
   <si>
     <t xml:space="preserve">cave_lerna</t>
@@ -1782,10 +1788,10 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C3" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="D3" t="s">
         <v>13</v>
@@ -1794,7 +1800,7 @@
         <v>14</v>
       </c>
       <c r="F3" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="G3" t="s">
         <v>15</v>
@@ -1810,10 +1816,10 @@
         <v>17</v>
       </c>
       <c r="B4" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C4" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="D4" t="s">
         <v>18</v>
@@ -1822,7 +1828,7 @@
         <v>19</v>
       </c>
       <c r="F4" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="G4" t="s">
         <v>20</v>
@@ -1838,10 +1844,10 @@
         <v>22</v>
       </c>
       <c r="B5" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C5" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="D5" t="s">
         <v>23</v>
@@ -1859,10 +1865,10 @@
         <v>25</v>
       </c>
       <c r="B6" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C6" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="D6" t="s">
         <v>26</v>
@@ -1880,10 +1886,10 @@
         <v>28</v>
       </c>
       <c r="B7" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C7" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="D7" t="s">
         <v>29</v>
@@ -1894,7 +1900,7 @@
       <c r="G7"/>
       <c r="H7"/>
       <c r="I7" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="J7" t="s">
         <v>31</v>
@@ -1908,10 +1914,10 @@
         <v>33</v>
       </c>
       <c r="B8" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C8" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="D8" t="s">
         <v>34</v>
@@ -1929,10 +1935,10 @@
         <v>36</v>
       </c>
       <c r="B9" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C9" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="D9" t="s">
         <v>37</v>
@@ -1941,7 +1947,7 @@
         <v>38</v>
       </c>
       <c r="F9" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="G9" t="s">
         <v>39</v>
@@ -1957,10 +1963,10 @@
         <v>41</v>
       </c>
       <c r="B10" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C10" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="D10" t="s">
         <v>42</v>
@@ -1978,10 +1984,10 @@
         <v>44</v>
       </c>
       <c r="B11" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C11" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="D11" t="s">
         <v>45</v>
@@ -1999,10 +2005,10 @@
         <v>47</v>
       </c>
       <c r="B12" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C12" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="D12" t="s">
         <v>48</v>
@@ -2020,10 +2026,10 @@
         <v>50</v>
       </c>
       <c r="B13" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C13" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="D13" t="s">
         <v>51</v>
@@ -2032,7 +2038,7 @@
         <v>52</v>
       </c>
       <c r="F13" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="G13" t="s">
         <v>53</v>
@@ -2048,10 +2054,10 @@
         <v>55</v>
       </c>
       <c r="B14" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C14" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="D14" t="s">
         <v>56</v>
@@ -2060,7 +2066,7 @@
         <v>57</v>
       </c>
       <c r="F14" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="G14" t="s">
         <v>58</v>
@@ -2076,10 +2082,10 @@
         <v>60</v>
       </c>
       <c r="B15" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C15" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="D15" t="s">
         <v>61</v>
@@ -2088,7 +2094,7 @@
         <v>62</v>
       </c>
       <c r="F15" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G15" t="s">
         <v>63</v>
@@ -2104,10 +2110,10 @@
         <v>65</v>
       </c>
       <c r="B16" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C16" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="D16" t="s">
         <v>66</v>
@@ -2116,7 +2122,7 @@
         <v>67</v>
       </c>
       <c r="F16" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="G16" t="s">
         <v>68</v>
@@ -2132,10 +2138,10 @@
         <v>70</v>
       </c>
       <c r="B17" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C17" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="D17" t="s">
         <v>71</v>
@@ -2153,10 +2159,10 @@
         <v>73</v>
       </c>
       <c r="B18" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C18" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="D18" t="s">
         <v>51</v>
@@ -2165,7 +2171,7 @@
         <v>74</v>
       </c>
       <c r="F18" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="G18" t="s">
         <v>75</v>
@@ -2181,10 +2187,10 @@
         <v>77</v>
       </c>
       <c r="B19" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C19" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="D19" t="s">
         <v>78</v>
@@ -2202,10 +2208,10 @@
         <v>80</v>
       </c>
       <c r="B20" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="C20" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="D20" t="s">
         <v>81</v>
@@ -2223,10 +2229,10 @@
         <v>83</v>
       </c>
       <c r="B21" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C21" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="D21" t="s">
         <v>84</v>
@@ -2244,10 +2250,10 @@
         <v>86</v>
       </c>
       <c r="B22" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C22" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="D22" t="s">
         <v>87</v>
@@ -2265,10 +2271,10 @@
         <v>89</v>
       </c>
       <c r="B23" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C23" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="D23" t="s">
         <v>90</v>
@@ -2286,10 +2292,10 @@
         <v>92</v>
       </c>
       <c r="B24" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C24" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="D24" t="s">
         <v>93</v>
@@ -2307,10 +2313,10 @@
         <v>95</v>
       </c>
       <c r="B25" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="C25" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="D25" t="s">
         <v>96</v>
@@ -2328,10 +2334,10 @@
         <v>98</v>
       </c>
       <c r="B26" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C26" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="D26" t="s">
         <v>99</v>
@@ -2342,7 +2348,7 @@
       <c r="G26"/>
       <c r="H26"/>
       <c r="I26" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="J26" t="s">
         <v>101</v>
@@ -2356,10 +2362,10 @@
         <v>103</v>
       </c>
       <c r="B27" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C27" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="D27" t="s">
         <v>104</v>
@@ -2370,7 +2376,7 @@
       <c r="G27"/>
       <c r="H27"/>
       <c r="I27" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="J27" t="s">
         <v>106</v>
@@ -2384,10 +2390,10 @@
         <v>108</v>
       </c>
       <c r="B28" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C28" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="D28" t="s">
         <v>109</v>
@@ -2398,7 +2404,7 @@
       <c r="G28"/>
       <c r="H28"/>
       <c r="I28" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="J28" t="s">
         <v>111</v>
@@ -2412,10 +2418,10 @@
         <v>113</v>
       </c>
       <c r="B29" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C29" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="D29" t="s">
         <v>114</v>
@@ -2433,10 +2439,10 @@
         <v>116</v>
       </c>
       <c r="B30" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C30" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="D30" t="s">
         <v>117</v>
@@ -2454,10 +2460,10 @@
         <v>119</v>
       </c>
       <c r="B31" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C31" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="D31" t="s">
         <v>120</v>
@@ -2468,7 +2474,7 @@
       <c r="G31"/>
       <c r="H31"/>
       <c r="I31" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="J31" t="s">
         <v>122</v>
@@ -2482,10 +2488,10 @@
         <v>124</v>
       </c>
       <c r="B32" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C32" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="D32" t="s">
         <v>125</v>
@@ -2496,7 +2502,7 @@
       <c r="G32"/>
       <c r="H32"/>
       <c r="I32" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="J32" t="s">
         <v>127</v>
@@ -2510,10 +2516,10 @@
         <v>129</v>
       </c>
       <c r="B33" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C33" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="D33" t="s">
         <v>130</v>
@@ -2531,10 +2537,10 @@
         <v>132</v>
       </c>
       <c r="B34" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C34" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="D34" t="s">
         <v>133</v>
@@ -2552,10 +2558,10 @@
         <v>135</v>
       </c>
       <c r="B35" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C35" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="D35" t="s">
         <v>136</v>
@@ -2573,10 +2579,10 @@
         <v>138</v>
       </c>
       <c r="B36" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C36" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="D36" t="s">
         <v>139</v>
@@ -2594,10 +2600,10 @@
         <v>141</v>
       </c>
       <c r="B37" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C37" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="D37" t="s">
         <v>142</v>
@@ -2608,7 +2614,7 @@
       <c r="G37"/>
       <c r="H37"/>
       <c r="I37" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="J37" t="s">
         <v>144</v>
@@ -2622,10 +2628,10 @@
         <v>146</v>
       </c>
       <c r="B38" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C38" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="D38" t="s">
         <v>147</v>
@@ -2636,7 +2642,7 @@
       <c r="G38"/>
       <c r="H38"/>
       <c r="I38" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="J38" t="s">
         <v>149</v>
@@ -2650,10 +2656,10 @@
         <v>151</v>
       </c>
       <c r="B39" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C39" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="D39" t="s">
         <v>152</v>
@@ -2671,10 +2677,10 @@
         <v>154</v>
       </c>
       <c r="B40" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="C40" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="D40" t="s">
         <v>155</v>
@@ -2692,10 +2698,10 @@
         <v>157</v>
       </c>
       <c r="B41" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C41" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="D41" t="s">
         <v>158</v>
@@ -2706,7 +2712,7 @@
       <c r="G41"/>
       <c r="H41"/>
       <c r="I41" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="J41" t="s">
         <v>160</v>
@@ -2720,10 +2726,10 @@
         <v>162</v>
       </c>
       <c r="B42" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="C42" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="D42" t="s">
         <v>163</v>
@@ -2734,7 +2740,7 @@
       <c r="G42"/>
       <c r="H42"/>
       <c r="I42" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="J42" t="s">
         <v>165</v>
@@ -2748,10 +2754,10 @@
         <v>167</v>
       </c>
       <c r="B43" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="C43" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="D43" t="s">
         <v>168</v>
@@ -2762,7 +2768,7 @@
       <c r="G43"/>
       <c r="H43"/>
       <c r="I43" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="J43" t="s">
         <v>170</v>
@@ -2776,10 +2782,10 @@
         <v>172</v>
       </c>
       <c r="B44" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C44" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="D44" t="s">
         <v>173</v>
@@ -2790,7 +2796,7 @@
       <c r="G44"/>
       <c r="H44"/>
       <c r="I44" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="J44" t="s">
         <v>175</v>
@@ -2804,10 +2810,10 @@
         <v>177</v>
       </c>
       <c r="B45" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="C45" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="D45" t="s">
         <v>178</v>
@@ -2818,7 +2824,7 @@
       <c r="G45"/>
       <c r="H45"/>
       <c r="I45" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="J45" t="s">
         <v>180</v>
@@ -2832,10 +2838,10 @@
         <v>182</v>
       </c>
       <c r="B46" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="C46" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="D46" t="s">
         <v>183</v>
@@ -2846,7 +2852,7 @@
       <c r="G46"/>
       <c r="H46"/>
       <c r="I46" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="J46" t="s">
         <v>185</v>
@@ -2860,10 +2866,10 @@
         <v>187</v>
       </c>
       <c r="B47" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C47" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="D47" t="s">
         <v>188</v>
@@ -2874,7 +2880,7 @@
       <c r="G47"/>
       <c r="H47"/>
       <c r="I47" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="J47" t="s">
         <v>190</v>
@@ -2888,10 +2894,10 @@
         <v>192</v>
       </c>
       <c r="B48" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C48" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="D48" t="s">
         <v>193</v>
@@ -2902,7 +2908,7 @@
       <c r="G48"/>
       <c r="H48"/>
       <c r="I48" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="J48" t="s">
         <v>195</v>
@@ -2916,10 +2922,10 @@
         <v>197</v>
       </c>
       <c r="B49" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C49" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="D49" t="s">
         <v>198</v>
@@ -2930,7 +2936,7 @@
       <c r="G49"/>
       <c r="H49"/>
       <c r="I49" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="J49" t="s">
         <v>200</v>
@@ -2944,10 +2950,10 @@
         <v>202</v>
       </c>
       <c r="B50" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C50" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="D50" t="s">
         <v>203</v>
@@ -2958,7 +2964,7 @@
       <c r="G50"/>
       <c r="H50"/>
       <c r="I50" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="J50" t="s">
         <v>205</v>
@@ -2972,10 +2978,10 @@
         <v>207</v>
       </c>
       <c r="B51" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C51" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="D51" t="s">
         <v>208</v>
@@ -2993,10 +2999,10 @@
         <v>210</v>
       </c>
       <c r="B52" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C52" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="D52" t="s">
         <v>211</v>
@@ -3007,7 +3013,7 @@
       <c r="G52"/>
       <c r="H52"/>
       <c r="I52" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="J52" t="s">
         <v>213</v>
@@ -3021,10 +3027,10 @@
         <v>215</v>
       </c>
       <c r="B53" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C53" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="D53" t="s">
         <v>216</v>
@@ -3042,10 +3048,10 @@
         <v>218</v>
       </c>
       <c r="B54" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C54" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="D54" t="s">
         <v>219</v>
@@ -3063,10 +3069,10 @@
         <v>221</v>
       </c>
       <c r="B55" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C55" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="D55" t="s">
         <v>222</v>
@@ -3077,7 +3083,7 @@
       <c r="G55"/>
       <c r="H55"/>
       <c r="I55" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="J55" t="s">
         <v>224</v>
@@ -3091,10 +3097,10 @@
         <v>226</v>
       </c>
       <c r="B56" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C56" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="D56" t="s">
         <v>227</v>
@@ -3112,10 +3118,10 @@
         <v>229</v>
       </c>
       <c r="B57" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="C57" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="D57" t="s">
         <v>230</v>
@@ -3133,10 +3139,10 @@
         <v>232</v>
       </c>
       <c r="B58" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C58" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="D58" t="s">
         <v>233</v>
@@ -3146,24 +3152,28 @@
       </c>
       <c r="G58"/>
       <c r="H58"/>
-      <c r="J58"/>
-      <c r="K58"/>
+      <c r="J58" t="s">
+        <v>235</v>
+      </c>
+      <c r="K58" t="s">
+        <v>236</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B59" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C59" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="D59" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="E59" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="G59"/>
       <c r="H59"/>
@@ -3172,19 +3182,19 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B60" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C60" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="D60" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="E60" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="G60"/>
       <c r="H60"/>
@@ -3193,19 +3203,19 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B61" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C61" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="D61" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="E61" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="G61"/>
       <c r="H61"/>
@@ -3214,131 +3224,131 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B62" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C62" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="D62" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="E62" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="G62"/>
       <c r="H62"/>
       <c r="I62" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="J62" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="K62" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B63" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C63" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="D63" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="E63" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="G63"/>
       <c r="H63"/>
       <c r="I63" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="J63" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="K63" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B64" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C64" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="D64" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="E64" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="G64"/>
       <c r="H64"/>
       <c r="I64" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="J64" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="K64" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B65" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C65" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="D65" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="E65" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="G65"/>
       <c r="H65"/>
       <c r="I65" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="J65" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="K65" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B66" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="C66" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="D66" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="E66" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="G66"/>
       <c r="H66"/>
@@ -3347,103 +3357,103 @@
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B67" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="C67" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="D67" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E67" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="G67"/>
       <c r="H67"/>
       <c r="I67" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="J67" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="K67" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B68" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C68" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="D68" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="E68" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="G68"/>
       <c r="H68"/>
       <c r="I68" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="J68" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="K68" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B69" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C69" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="D69" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="E69" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="G69"/>
       <c r="H69"/>
       <c r="I69" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="J69" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="K69" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B70" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="C70" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="D70" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="E70" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="G70"/>
       <c r="H70"/>
@@ -3452,19 +3462,19 @@
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B71" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="C71" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="D71" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="E71" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="G71"/>
       <c r="H71"/>
@@ -3473,47 +3483,47 @@
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B72" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C72" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="D72" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="E72" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="G72"/>
       <c r="H72"/>
       <c r="I72" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="J72" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="K72" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B73" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C73" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="D73" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="E73" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="G73"/>
       <c r="H73"/>
@@ -3522,75 +3532,75 @@
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B74" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C74" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="D74" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="E74" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="G74"/>
       <c r="H74"/>
       <c r="I74" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="J74" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="K74" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B75" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C75" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="D75" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="E75" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="G75"/>
       <c r="H75"/>
       <c r="I75" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="J75" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="K75" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B76" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C76" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="D76" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="E76" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="G76"/>
       <c r="H76"/>
@@ -3599,131 +3609,131 @@
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B77" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C77" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="D77" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="E77" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="G77"/>
       <c r="H77"/>
       <c r="I77" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="J77" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="K77" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B78" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="C78" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="D78" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="E78" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="G78"/>
       <c r="H78"/>
       <c r="I78" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="J78" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="K78" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B79" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="C79" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="D79" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="E79" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="G79"/>
       <c r="H79"/>
       <c r="I79" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="J79" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="K79" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="B80" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C80" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="D80" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="E80" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="G80"/>
       <c r="H80"/>
       <c r="I80" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="J80" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="K80" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B81" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C81" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="D81" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="E81" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="G81"/>
       <c r="H81"/>
@@ -3732,19 +3742,19 @@
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="B82" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C82" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="D82" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E82" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="G82"/>
       <c r="H82"/>
@@ -3753,13 +3763,13 @@
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="B83" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C83" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="D83" t="s">
         <v>99</v>
@@ -3774,13 +3784,13 @@
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B84" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C84" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="D84" t="s">
         <v>99</v>
@@ -3795,19 +3805,19 @@
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B85" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C85" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="D85" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="E85" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="G85"/>
       <c r="H85"/>
@@ -3816,19 +3826,19 @@
     </row>
     <row r="86">
       <c r="A86" t="s">
+        <v>340</v>
+      </c>
+      <c r="B86" t="s">
+        <v>407</v>
+      </c>
+      <c r="C86" t="s">
+        <v>492</v>
+      </c>
+      <c r="D86" t="s">
         <v>338</v>
       </c>
-      <c r="B86" t="s">
-        <v>405</v>
-      </c>
-      <c r="C86" t="s">
-        <v>490</v>
-      </c>
-      <c r="D86" t="s">
-        <v>336</v>
-      </c>
       <c r="E86" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="G86"/>
       <c r="H86"/>
@@ -3837,19 +3847,19 @@
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B87" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C87" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="D87" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="E87" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="G87"/>
       <c r="H87"/>
@@ -3858,19 +3868,19 @@
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B88" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="C88" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="D88" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="E88" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="G88"/>
       <c r="H88"/>
@@ -3879,19 +3889,19 @@
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B89" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C89" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="D89" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="E89" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="G89"/>
       <c r="H89"/>
@@ -3900,19 +3910,19 @@
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B90" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C90" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="D90" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="E90" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="G90"/>
       <c r="H90"/>
@@ -3921,19 +3931,19 @@
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B91" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="C91" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="D91" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="E91" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="G91"/>
       <c r="H91"/>
@@ -3942,19 +3952,19 @@
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="B92" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="C92" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="D92" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="E92" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="G92"/>
       <c r="H92"/>
@@ -3963,19 +3973,19 @@
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B93" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C93" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="D93" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="E93" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="G93"/>
       <c r="H93"/>
@@ -3984,19 +3994,19 @@
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B94" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="C94" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="D94" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="E94" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="G94"/>
       <c r="H94"/>
@@ -4005,19 +4015,19 @@
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B95" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="C95" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="D95" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="E95" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="G95"/>
       <c r="H95"/>
@@ -4026,19 +4036,19 @@
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B96" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C96" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="D96" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="E96" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="G96"/>
       <c r="H96"/>
@@ -4047,19 +4057,19 @@
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B97" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C97" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="D97" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="E97" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="G97"/>
       <c r="H97"/>
@@ -4068,19 +4078,19 @@
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B98" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="C98" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="D98" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="E98" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="G98"/>
       <c r="H98"/>
@@ -4089,19 +4099,19 @@
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="B99" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="C99" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="D99" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="E99" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="G99"/>
       <c r="H99"/>
@@ -4110,19 +4120,19 @@
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="B100" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C100" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="D100" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="E100" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="G100"/>
       <c r="H100"/>
@@ -4131,19 +4141,19 @@
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B101" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C101" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="D101" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="E101" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="G101"/>
       <c r="H101"/>
@@ -4152,30 +4162,30 @@
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B102" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C102" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="D102" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="E102" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="G102"/>
       <c r="H102"/>
       <c r="I102" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="J102" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="K102" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
   </sheetData>

--- a/Mod_Korean/Lang/KR/Game/Zone.xlsx
+++ b/Mod_Korean/Lang/KR/Game/Zone.xlsx
@@ -53,7 +53,7 @@
     <t xml:space="preserve">world</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.252</t>
+    <t xml:space="preserve">EA 23.260</t>
   </si>
   <si>
     <t xml:space="preserve">Ylva</t>

--- a/Mod_Korean/Lang/KR/Game/Zone.xlsx
+++ b/Mod_Korean/Lang/KR/Game/Zone.xlsx
@@ -53,7 +53,7 @@
     <t xml:space="preserve">world</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.260</t>
+    <t xml:space="preserve">EA 23.267</t>
   </si>
   <si>
     <t xml:space="preserve">Ylva</t>

--- a/Mod_Korean/Lang/KR/Game/Zone.xlsx
+++ b/Mod_Korean/Lang/KR/Game/Zone.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="743" uniqueCount="552">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="751" uniqueCount="556">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -53,7 +53,7 @@
     <t xml:space="preserve">world</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.267</t>
+    <t xml:space="preserve">EA 23.281</t>
   </si>
   <si>
     <t xml:space="preserve">Ylva</t>
@@ -704,6 +704,15 @@
     <t xml:space="preserve">古城</t>
   </si>
   <si>
+    <t xml:space="preserve">oldchurch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Old Church</t>
+  </si>
+  <si>
+    <t xml:space="preserve">古い教会</t>
+  </si>
+  <si>
     <t xml:space="preserve">keep_seeker</t>
   </si>
   <si>
@@ -1092,6 +1101,9 @@
   </si>
   <si>
     <t xml:space="preserve">演奏会場</t>
+  </si>
+  <si>
+    <t xml:space="preserve">instance_wedding</t>
   </si>
   <si>
     <t xml:space="preserve">dungeon</t>
@@ -1791,10 +1803,10 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C3" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="D3" t="s">
         <v>13</v>
@@ -1803,7 +1815,7 @@
         <v>14</v>
       </c>
       <c r="F3" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="G3" t="s">
         <v>15</v>
@@ -1819,10 +1831,10 @@
         <v>17</v>
       </c>
       <c r="B4" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C4" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="D4" t="s">
         <v>18</v>
@@ -1831,7 +1843,7 @@
         <v>19</v>
       </c>
       <c r="F4" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="G4" t="s">
         <v>20</v>
@@ -1847,10 +1859,10 @@
         <v>22</v>
       </c>
       <c r="B5" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C5" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="D5" t="s">
         <v>23</v>
@@ -1868,10 +1880,10 @@
         <v>25</v>
       </c>
       <c r="B6" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C6" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="D6" t="s">
         <v>26</v>
@@ -1889,10 +1901,10 @@
         <v>28</v>
       </c>
       <c r="B7" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C7" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="D7" t="s">
         <v>29</v>
@@ -1903,7 +1915,7 @@
       <c r="G7"/>
       <c r="H7"/>
       <c r="I7" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="J7" t="s">
         <v>31</v>
@@ -1917,10 +1929,10 @@
         <v>33</v>
       </c>
       <c r="B8" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="C8" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="D8" t="s">
         <v>34</v>
@@ -1938,10 +1950,10 @@
         <v>36</v>
       </c>
       <c r="B9" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C9" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="D9" t="s">
         <v>37</v>
@@ -1950,7 +1962,7 @@
         <v>38</v>
       </c>
       <c r="F9" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="G9" t="s">
         <v>39</v>
@@ -1966,10 +1978,10 @@
         <v>41</v>
       </c>
       <c r="B10" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C10" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="D10" t="s">
         <v>42</v>
@@ -1987,10 +1999,10 @@
         <v>44</v>
       </c>
       <c r="B11" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C11" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="D11" t="s">
         <v>45</v>
@@ -2008,10 +2020,10 @@
         <v>47</v>
       </c>
       <c r="B12" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C12" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="D12" t="s">
         <v>48</v>
@@ -2029,10 +2041,10 @@
         <v>50</v>
       </c>
       <c r="B13" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C13" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="D13" t="s">
         <v>51</v>
@@ -2041,7 +2053,7 @@
         <v>52</v>
       </c>
       <c r="F13" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="G13" t="s">
         <v>53</v>
@@ -2057,10 +2069,10 @@
         <v>55</v>
       </c>
       <c r="B14" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C14" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="D14" t="s">
         <v>56</v>
@@ -2069,7 +2081,7 @@
         <v>57</v>
       </c>
       <c r="F14" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="G14" t="s">
         <v>58</v>
@@ -2085,10 +2097,10 @@
         <v>60</v>
       </c>
       <c r="B15" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C15" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="D15" t="s">
         <v>61</v>
@@ -2097,7 +2109,7 @@
         <v>62</v>
       </c>
       <c r="F15" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="G15" t="s">
         <v>63</v>
@@ -2113,10 +2125,10 @@
         <v>65</v>
       </c>
       <c r="B16" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C16" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="D16" t="s">
         <v>66</v>
@@ -2125,7 +2137,7 @@
         <v>67</v>
       </c>
       <c r="F16" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="G16" t="s">
         <v>68</v>
@@ -2141,10 +2153,10 @@
         <v>70</v>
       </c>
       <c r="B17" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="C17" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="D17" t="s">
         <v>71</v>
@@ -2162,10 +2174,10 @@
         <v>73</v>
       </c>
       <c r="B18" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C18" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="D18" t="s">
         <v>51</v>
@@ -2174,7 +2186,7 @@
         <v>74</v>
       </c>
       <c r="F18" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="G18" t="s">
         <v>75</v>
@@ -2190,10 +2202,10 @@
         <v>77</v>
       </c>
       <c r="B19" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C19" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="D19" t="s">
         <v>78</v>
@@ -2211,10 +2223,10 @@
         <v>80</v>
       </c>
       <c r="B20" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="C20" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="D20" t="s">
         <v>81</v>
@@ -2232,10 +2244,10 @@
         <v>83</v>
       </c>
       <c r="B21" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="C21" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="D21" t="s">
         <v>84</v>
@@ -2253,10 +2265,10 @@
         <v>86</v>
       </c>
       <c r="B22" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="C22" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="D22" t="s">
         <v>87</v>
@@ -2274,10 +2286,10 @@
         <v>89</v>
       </c>
       <c r="B23" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C23" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="D23" t="s">
         <v>90</v>
@@ -2295,10 +2307,10 @@
         <v>92</v>
       </c>
       <c r="B24" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C24" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="D24" t="s">
         <v>93</v>
@@ -2316,10 +2328,10 @@
         <v>95</v>
       </c>
       <c r="B25" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="C25" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="D25" t="s">
         <v>96</v>
@@ -2337,10 +2349,10 @@
         <v>98</v>
       </c>
       <c r="B26" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C26" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="D26" t="s">
         <v>99</v>
@@ -2351,7 +2363,7 @@
       <c r="G26"/>
       <c r="H26"/>
       <c r="I26" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="J26" t="s">
         <v>101</v>
@@ -2365,10 +2377,10 @@
         <v>103</v>
       </c>
       <c r="B27" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C27" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="D27" t="s">
         <v>104</v>
@@ -2379,7 +2391,7 @@
       <c r="G27"/>
       <c r="H27"/>
       <c r="I27" t="s">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="J27" t="s">
         <v>106</v>
@@ -2393,10 +2405,10 @@
         <v>108</v>
       </c>
       <c r="B28" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="C28" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="D28" t="s">
         <v>109</v>
@@ -2407,7 +2419,7 @@
       <c r="G28"/>
       <c r="H28"/>
       <c r="I28" t="s">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="J28" t="s">
         <v>111</v>
@@ -2421,10 +2433,10 @@
         <v>113</v>
       </c>
       <c r="B29" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C29" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="D29" t="s">
         <v>114</v>
@@ -2442,10 +2454,10 @@
         <v>116</v>
       </c>
       <c r="B30" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C30" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="D30" t="s">
         <v>117</v>
@@ -2463,10 +2475,10 @@
         <v>119</v>
       </c>
       <c r="B31" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C31" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="D31" t="s">
         <v>120</v>
@@ -2477,7 +2489,7 @@
       <c r="G31"/>
       <c r="H31"/>
       <c r="I31" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="J31" t="s">
         <v>122</v>
@@ -2491,10 +2503,10 @@
         <v>124</v>
       </c>
       <c r="B32" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C32" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="D32" t="s">
         <v>125</v>
@@ -2505,7 +2517,7 @@
       <c r="G32"/>
       <c r="H32"/>
       <c r="I32" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="J32" t="s">
         <v>127</v>
@@ -2519,10 +2531,10 @@
         <v>129</v>
       </c>
       <c r="B33" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C33" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="D33" t="s">
         <v>130</v>
@@ -2540,10 +2552,10 @@
         <v>132</v>
       </c>
       <c r="B34" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C34" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="D34" t="s">
         <v>133</v>
@@ -2561,10 +2573,10 @@
         <v>135</v>
       </c>
       <c r="B35" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C35" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="D35" t="s">
         <v>136</v>
@@ -2582,10 +2594,10 @@
         <v>138</v>
       </c>
       <c r="B36" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C36" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="D36" t="s">
         <v>139</v>
@@ -2603,10 +2615,10 @@
         <v>141</v>
       </c>
       <c r="B37" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C37" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="D37" t="s">
         <v>142</v>
@@ -2617,7 +2629,7 @@
       <c r="G37"/>
       <c r="H37"/>
       <c r="I37" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="J37" t="s">
         <v>144</v>
@@ -2631,10 +2643,10 @@
         <v>146</v>
       </c>
       <c r="B38" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C38" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="D38" t="s">
         <v>147</v>
@@ -2645,7 +2657,7 @@
       <c r="G38"/>
       <c r="H38"/>
       <c r="I38" t="s">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="J38" t="s">
         <v>149</v>
@@ -2659,10 +2671,10 @@
         <v>151</v>
       </c>
       <c r="B39" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C39" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="D39" t="s">
         <v>152</v>
@@ -2680,10 +2692,10 @@
         <v>154</v>
       </c>
       <c r="B40" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="C40" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="D40" t="s">
         <v>155</v>
@@ -2701,10 +2713,10 @@
         <v>157</v>
       </c>
       <c r="B41" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C41" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="D41" t="s">
         <v>158</v>
@@ -2715,7 +2727,7 @@
       <c r="G41"/>
       <c r="H41"/>
       <c r="I41" t="s">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="J41" t="s">
         <v>160</v>
@@ -2729,10 +2741,10 @@
         <v>162</v>
       </c>
       <c r="B42" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="C42" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="D42" t="s">
         <v>163</v>
@@ -2743,7 +2755,7 @@
       <c r="G42"/>
       <c r="H42"/>
       <c r="I42" t="s">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="J42" t="s">
         <v>165</v>
@@ -2757,10 +2769,10 @@
         <v>167</v>
       </c>
       <c r="B43" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="C43" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="D43" t="s">
         <v>168</v>
@@ -2771,7 +2783,7 @@
       <c r="G43"/>
       <c r="H43"/>
       <c r="I43" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="J43" t="s">
         <v>170</v>
@@ -2785,10 +2797,10 @@
         <v>172</v>
       </c>
       <c r="B44" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="C44" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="D44" t="s">
         <v>173</v>
@@ -2799,7 +2811,7 @@
       <c r="G44"/>
       <c r="H44"/>
       <c r="I44" t="s">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="J44" t="s">
         <v>175</v>
@@ -2813,10 +2825,10 @@
         <v>177</v>
       </c>
       <c r="B45" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="C45" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="D45" t="s">
         <v>178</v>
@@ -2827,7 +2839,7 @@
       <c r="G45"/>
       <c r="H45"/>
       <c r="I45" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="J45" t="s">
         <v>180</v>
@@ -2841,10 +2853,10 @@
         <v>182</v>
       </c>
       <c r="B46" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="C46" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="D46" t="s">
         <v>183</v>
@@ -2855,7 +2867,7 @@
       <c r="G46"/>
       <c r="H46"/>
       <c r="I46" t="s">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="J46" t="s">
         <v>185</v>
@@ -2869,10 +2881,10 @@
         <v>187</v>
       </c>
       <c r="B47" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C47" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="D47" t="s">
         <v>188</v>
@@ -2883,7 +2895,7 @@
       <c r="G47"/>
       <c r="H47"/>
       <c r="I47" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="J47" t="s">
         <v>190</v>
@@ -2897,10 +2909,10 @@
         <v>192</v>
       </c>
       <c r="B48" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C48" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="D48" t="s">
         <v>193</v>
@@ -2911,7 +2923,7 @@
       <c r="G48"/>
       <c r="H48"/>
       <c r="I48" t="s">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="J48" t="s">
         <v>195</v>
@@ -2925,10 +2937,10 @@
         <v>197</v>
       </c>
       <c r="B49" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C49" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="D49" t="s">
         <v>198</v>
@@ -2939,7 +2951,7 @@
       <c r="G49"/>
       <c r="H49"/>
       <c r="I49" t="s">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="J49" t="s">
         <v>200</v>
@@ -2953,10 +2965,10 @@
         <v>202</v>
       </c>
       <c r="B50" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C50" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="D50" t="s">
         <v>203</v>
@@ -2967,7 +2979,7 @@
       <c r="G50"/>
       <c r="H50"/>
       <c r="I50" t="s">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="J50" t="s">
         <v>205</v>
@@ -2981,10 +2993,10 @@
         <v>207</v>
       </c>
       <c r="B51" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C51" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="D51" t="s">
         <v>208</v>
@@ -3002,10 +3014,10 @@
         <v>210</v>
       </c>
       <c r="B52" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C52" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="D52" t="s">
         <v>211</v>
@@ -3016,7 +3028,7 @@
       <c r="G52"/>
       <c r="H52"/>
       <c r="I52" t="s">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="J52" t="s">
         <v>213</v>
@@ -3030,10 +3042,10 @@
         <v>215</v>
       </c>
       <c r="B53" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C53" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="D53" t="s">
         <v>216</v>
@@ -3051,10 +3063,10 @@
         <v>218</v>
       </c>
       <c r="B54" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C54" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="D54" t="s">
         <v>219</v>
@@ -3072,10 +3084,10 @@
         <v>221</v>
       </c>
       <c r="B55" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C55" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="D55" t="s">
         <v>222</v>
@@ -3086,7 +3098,7 @@
       <c r="G55"/>
       <c r="H55"/>
       <c r="I55" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="J55" t="s">
         <v>224</v>
@@ -3100,10 +3112,10 @@
         <v>226</v>
       </c>
       <c r="B56" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C56" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="D56" t="s">
         <v>227</v>
@@ -3121,10 +3133,7 @@
         <v>229</v>
       </c>
       <c r="B57" t="s">
-        <v>402</v>
-      </c>
-      <c r="C57" t="s">
-        <v>467</v>
+        <v>12</v>
       </c>
       <c r="D57" t="s">
         <v>230</v>
@@ -3142,10 +3151,10 @@
         <v>232</v>
       </c>
       <c r="B58" t="s">
-        <v>390</v>
+        <v>406</v>
       </c>
       <c r="C58" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="D58" t="s">
         <v>233</v>
@@ -3155,46 +3164,46 @@
       </c>
       <c r="G58"/>
       <c r="H58"/>
-      <c r="I58" t="s">
-        <v>536</v>
-      </c>
-      <c r="J58" t="s">
-        <v>235</v>
-      </c>
-      <c r="K58" t="s">
-        <v>236</v>
-      </c>
+      <c r="J58"/>
+      <c r="K58"/>
     </row>
     <row r="59">
       <c r="A59" t="s">
+        <v>235</v>
+      </c>
+      <c r="B59" t="s">
+        <v>394</v>
+      </c>
+      <c r="C59" t="s">
+        <v>472</v>
+      </c>
+      <c r="D59" t="s">
+        <v>236</v>
+      </c>
+      <c r="E59" t="s">
         <v>237</v>
-      </c>
-      <c r="B59" t="s">
-        <v>390</v>
-      </c>
-      <c r="C59" t="s">
-        <v>469</v>
-      </c>
-      <c r="D59" t="s">
-        <v>238</v>
-      </c>
-      <c r="E59" t="s">
-        <v>239</v>
       </c>
       <c r="G59"/>
       <c r="H59"/>
-      <c r="J59"/>
-      <c r="K59"/>
+      <c r="I59" t="s">
+        <v>540</v>
+      </c>
+      <c r="J59" t="s">
+        <v>238</v>
+      </c>
+      <c r="K59" t="s">
+        <v>239</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
         <v>240</v>
       </c>
       <c r="B60" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C60" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="D60" t="s">
         <v>241</v>
@@ -3212,10 +3221,10 @@
         <v>243</v>
       </c>
       <c r="B61" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C61" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="D61" t="s">
         <v>244</v>
@@ -3233,10 +3242,10 @@
         <v>246</v>
       </c>
       <c r="B62" t="s">
-        <v>403</v>
+        <v>394</v>
       </c>
       <c r="C62" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="D62" t="s">
         <v>247</v>
@@ -3246,130 +3255,130 @@
       </c>
       <c r="G62"/>
       <c r="H62"/>
-      <c r="I62" t="s">
-        <v>537</v>
-      </c>
-      <c r="J62" t="s">
-        <v>249</v>
-      </c>
-      <c r="K62" t="s">
-        <v>250</v>
-      </c>
+      <c r="J62"/>
+      <c r="K62"/>
     </row>
     <row r="63">
       <c r="A63" t="s">
+        <v>249</v>
+      </c>
+      <c r="B63" t="s">
+        <v>407</v>
+      </c>
+      <c r="C63" t="s">
+        <v>476</v>
+      </c>
+      <c r="D63" t="s">
+        <v>250</v>
+      </c>
+      <c r="E63" t="s">
         <v>251</v>
-      </c>
-      <c r="B63" t="s">
-        <v>390</v>
-      </c>
-      <c r="C63" t="s">
-        <v>473</v>
-      </c>
-      <c r="D63" t="s">
-        <v>252</v>
-      </c>
-      <c r="E63" t="s">
-        <v>253</v>
       </c>
       <c r="G63"/>
       <c r="H63"/>
       <c r="I63" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="J63" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="K63" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
+        <v>254</v>
+      </c>
+      <c r="B64" t="s">
+        <v>394</v>
+      </c>
+      <c r="C64" t="s">
+        <v>477</v>
+      </c>
+      <c r="D64" t="s">
+        <v>255</v>
+      </c>
+      <c r="E64" t="s">
         <v>256</v>
-      </c>
-      <c r="B64" t="s">
-        <v>390</v>
-      </c>
-      <c r="C64" t="s">
-        <v>474</v>
-      </c>
-      <c r="D64" t="s">
-        <v>257</v>
-      </c>
-      <c r="E64" t="s">
-        <v>258</v>
       </c>
       <c r="G64"/>
       <c r="H64"/>
       <c r="I64" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="J64" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="K64" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
+        <v>259</v>
+      </c>
+      <c r="B65" t="s">
+        <v>394</v>
+      </c>
+      <c r="C65" t="s">
+        <v>478</v>
+      </c>
+      <c r="D65" t="s">
+        <v>260</v>
+      </c>
+      <c r="E65" t="s">
         <v>261</v>
-      </c>
-      <c r="B65" t="s">
-        <v>390</v>
-      </c>
-      <c r="C65" t="s">
-        <v>475</v>
-      </c>
-      <c r="D65" t="s">
-        <v>262</v>
-      </c>
-      <c r="E65" t="s">
-        <v>263</v>
       </c>
       <c r="G65"/>
       <c r="H65"/>
       <c r="I65" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="J65" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="K65" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
+        <v>264</v>
+      </c>
+      <c r="B66" t="s">
+        <v>394</v>
+      </c>
+      <c r="C66" t="s">
+        <v>479</v>
+      </c>
+      <c r="D66" t="s">
+        <v>265</v>
+      </c>
+      <c r="E66" t="s">
         <v>266</v>
-      </c>
-      <c r="B66" t="s">
-        <v>396</v>
-      </c>
-      <c r="C66" t="s">
-        <v>476</v>
-      </c>
-      <c r="D66" t="s">
-        <v>267</v>
-      </c>
-      <c r="E66" t="s">
-        <v>268</v>
       </c>
       <c r="G66"/>
       <c r="H66"/>
-      <c r="J66"/>
-      <c r="K66"/>
+      <c r="I66" t="s">
+        <v>544</v>
+      </c>
+      <c r="J66" t="s">
+        <v>267</v>
+      </c>
+      <c r="K66" t="s">
+        <v>268</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
         <v>269</v>
       </c>
       <c r="B67" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="C67" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="D67" t="s">
         <v>270</v>
@@ -3379,102 +3388,102 @@
       </c>
       <c r="G67"/>
       <c r="H67"/>
-      <c r="I67" t="s">
-        <v>541</v>
-      </c>
-      <c r="J67" t="s">
-        <v>272</v>
-      </c>
-      <c r="K67" t="s">
-        <v>273</v>
-      </c>
+      <c r="J67"/>
+      <c r="K67"/>
     </row>
     <row r="68">
       <c r="A68" t="s">
+        <v>272</v>
+      </c>
+      <c r="B68" t="s">
+        <v>408</v>
+      </c>
+      <c r="C68" t="s">
+        <v>481</v>
+      </c>
+      <c r="D68" t="s">
+        <v>273</v>
+      </c>
+      <c r="E68" t="s">
         <v>274</v>
-      </c>
-      <c r="B68" t="s">
-        <v>390</v>
-      </c>
-      <c r="C68" t="s">
-        <v>478</v>
-      </c>
-      <c r="D68" t="s">
-        <v>275</v>
-      </c>
-      <c r="E68" t="s">
-        <v>276</v>
       </c>
       <c r="G68"/>
       <c r="H68"/>
       <c r="I68" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="J68" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="K68" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
+        <v>277</v>
+      </c>
+      <c r="B69" t="s">
+        <v>394</v>
+      </c>
+      <c r="C69" t="s">
+        <v>482</v>
+      </c>
+      <c r="D69" t="s">
+        <v>278</v>
+      </c>
+      <c r="E69" t="s">
         <v>279</v>
-      </c>
-      <c r="B69" t="s">
-        <v>390</v>
-      </c>
-      <c r="C69" t="s">
-        <v>479</v>
-      </c>
-      <c r="D69" t="s">
-        <v>280</v>
-      </c>
-      <c r="E69" t="s">
-        <v>281</v>
       </c>
       <c r="G69"/>
       <c r="H69"/>
       <c r="I69" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="J69" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="K69" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
+        <v>282</v>
+      </c>
+      <c r="B70" t="s">
+        <v>394</v>
+      </c>
+      <c r="C70" t="s">
+        <v>483</v>
+      </c>
+      <c r="D70" t="s">
+        <v>283</v>
+      </c>
+      <c r="E70" t="s">
         <v>284</v>
-      </c>
-      <c r="B70" t="s">
-        <v>393</v>
-      </c>
-      <c r="C70" t="s">
-        <v>480</v>
-      </c>
-      <c r="D70" t="s">
-        <v>285</v>
-      </c>
-      <c r="E70" t="s">
-        <v>286</v>
       </c>
       <c r="G70"/>
       <c r="H70"/>
-      <c r="J70"/>
-      <c r="K70"/>
+      <c r="I70" t="s">
+        <v>547</v>
+      </c>
+      <c r="J70" t="s">
+        <v>285</v>
+      </c>
+      <c r="K70" t="s">
+        <v>286</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
         <v>287</v>
       </c>
       <c r="B71" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="C71" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="D71" t="s">
         <v>288</v>
@@ -3492,10 +3501,10 @@
         <v>290</v>
       </c>
       <c r="B72" t="s">
-        <v>390</v>
+        <v>397</v>
       </c>
       <c r="C72" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="D72" t="s">
         <v>291</v>
@@ -3505,46 +3514,46 @@
       </c>
       <c r="G72"/>
       <c r="H72"/>
-      <c r="I72" t="s">
-        <v>544</v>
-      </c>
-      <c r="J72" t="s">
-        <v>293</v>
-      </c>
-      <c r="K72" t="s">
-        <v>294</v>
-      </c>
+      <c r="J72"/>
+      <c r="K72"/>
     </row>
     <row r="73">
       <c r="A73" t="s">
+        <v>293</v>
+      </c>
+      <c r="B73" t="s">
+        <v>394</v>
+      </c>
+      <c r="C73" t="s">
+        <v>486</v>
+      </c>
+      <c r="D73" t="s">
+        <v>294</v>
+      </c>
+      <c r="E73" t="s">
         <v>295</v>
-      </c>
-      <c r="B73" t="s">
-        <v>390</v>
-      </c>
-      <c r="C73" t="s">
-        <v>483</v>
-      </c>
-      <c r="D73" t="s">
-        <v>296</v>
-      </c>
-      <c r="E73" t="s">
-        <v>297</v>
       </c>
       <c r="G73"/>
       <c r="H73"/>
-      <c r="J73"/>
-      <c r="K73"/>
+      <c r="I73" t="s">
+        <v>548</v>
+      </c>
+      <c r="J73" t="s">
+        <v>296</v>
+      </c>
+      <c r="K73" t="s">
+        <v>297</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
         <v>298</v>
       </c>
       <c r="B74" t="s">
-        <v>405</v>
+        <v>394</v>
       </c>
       <c r="C74" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="D74" t="s">
         <v>299</v>
@@ -3554,207 +3563,207 @@
       </c>
       <c r="G74"/>
       <c r="H74"/>
-      <c r="I74" t="s">
-        <v>545</v>
-      </c>
-      <c r="J74" t="s">
-        <v>301</v>
-      </c>
-      <c r="K74" t="s">
-        <v>302</v>
-      </c>
+      <c r="J74"/>
+      <c r="K74"/>
     </row>
     <row r="75">
       <c r="A75" t="s">
+        <v>301</v>
+      </c>
+      <c r="B75" t="s">
+        <v>409</v>
+      </c>
+      <c r="C75" t="s">
+        <v>488</v>
+      </c>
+      <c r="D75" t="s">
+        <v>302</v>
+      </c>
+      <c r="E75" t="s">
         <v>303</v>
-      </c>
-      <c r="B75" t="s">
-        <v>405</v>
-      </c>
-      <c r="C75" t="s">
-        <v>485</v>
-      </c>
-      <c r="D75" t="s">
-        <v>304</v>
-      </c>
-      <c r="E75" t="s">
-        <v>305</v>
       </c>
       <c r="G75"/>
       <c r="H75"/>
       <c r="I75" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="J75" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="K75" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
+        <v>306</v>
+      </c>
+      <c r="B76" t="s">
+        <v>409</v>
+      </c>
+      <c r="C76" t="s">
+        <v>489</v>
+      </c>
+      <c r="D76" t="s">
+        <v>307</v>
+      </c>
+      <c r="E76" t="s">
         <v>308</v>
-      </c>
-      <c r="B76" t="s">
-        <v>405</v>
-      </c>
-      <c r="C76" t="s">
-        <v>485</v>
-      </c>
-      <c r="D76" t="s">
-        <v>304</v>
-      </c>
-      <c r="E76" t="s">
-        <v>305</v>
       </c>
       <c r="G76"/>
       <c r="H76"/>
-      <c r="J76"/>
-      <c r="K76"/>
+      <c r="I76" t="s">
+        <v>550</v>
+      </c>
+      <c r="J76" t="s">
+        <v>309</v>
+      </c>
+      <c r="K76" t="s">
+        <v>310</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B77" t="s">
-        <v>390</v>
+        <v>409</v>
       </c>
       <c r="C77" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="D77" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="E77" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="G77"/>
       <c r="H77"/>
-      <c r="I77" t="s">
-        <v>547</v>
-      </c>
-      <c r="J77" t="s">
-        <v>312</v>
-      </c>
-      <c r="K77" t="s">
-        <v>313</v>
-      </c>
+      <c r="J77"/>
+      <c r="K77"/>
     </row>
     <row r="78">
       <c r="A78" t="s">
+        <v>312</v>
+      </c>
+      <c r="B78" t="s">
+        <v>394</v>
+      </c>
+      <c r="C78" t="s">
+        <v>490</v>
+      </c>
+      <c r="D78" t="s">
+        <v>313</v>
+      </c>
+      <c r="E78" t="s">
         <v>314</v>
-      </c>
-      <c r="B78" t="s">
-        <v>406</v>
-      </c>
-      <c r="C78" t="s">
-        <v>487</v>
-      </c>
-      <c r="D78" t="s">
-        <v>315</v>
-      </c>
-      <c r="E78" t="s">
-        <v>316</v>
       </c>
       <c r="G78"/>
       <c r="H78"/>
       <c r="I78" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="J78" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="K78" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s">
+        <v>317</v>
+      </c>
+      <c r="B79" t="s">
+        <v>410</v>
+      </c>
+      <c r="C79" t="s">
+        <v>491</v>
+      </c>
+      <c r="D79" t="s">
+        <v>318</v>
+      </c>
+      <c r="E79" t="s">
         <v>319</v>
-      </c>
-      <c r="B79" t="s">
-        <v>399</v>
-      </c>
-      <c r="C79" t="s">
-        <v>488</v>
-      </c>
-      <c r="D79" t="s">
-        <v>320</v>
-      </c>
-      <c r="E79" t="s">
-        <v>321</v>
       </c>
       <c r="G79"/>
       <c r="H79"/>
       <c r="I79" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="J79" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="K79" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
+        <v>322</v>
+      </c>
+      <c r="B80" t="s">
+        <v>403</v>
+      </c>
+      <c r="C80" t="s">
+        <v>492</v>
+      </c>
+      <c r="D80" t="s">
+        <v>323</v>
+      </c>
+      <c r="E80" t="s">
         <v>324</v>
-      </c>
-      <c r="B80" t="s">
-        <v>390</v>
-      </c>
-      <c r="C80" t="s">
-        <v>489</v>
-      </c>
-      <c r="D80" t="s">
-        <v>325</v>
-      </c>
-      <c r="E80" t="s">
-        <v>326</v>
       </c>
       <c r="G80"/>
       <c r="H80"/>
       <c r="I80" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="J80" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="K80" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s">
+        <v>327</v>
+      </c>
+      <c r="B81" t="s">
+        <v>394</v>
+      </c>
+      <c r="C81" t="s">
+        <v>493</v>
+      </c>
+      <c r="D81" t="s">
+        <v>328</v>
+      </c>
+      <c r="E81" t="s">
         <v>329</v>
-      </c>
-      <c r="B81" t="s">
-        <v>390</v>
-      </c>
-      <c r="C81" t="s">
-        <v>490</v>
-      </c>
-      <c r="D81" t="s">
-        <v>330</v>
-      </c>
-      <c r="E81" t="s">
-        <v>331</v>
       </c>
       <c r="G81"/>
       <c r="H81"/>
-      <c r="J81"/>
-      <c r="K81"/>
+      <c r="I81" t="s">
+        <v>554</v>
+      </c>
+      <c r="J81" t="s">
+        <v>330</v>
+      </c>
+      <c r="K81" t="s">
+        <v>331</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="s">
         <v>332</v>
       </c>
       <c r="B82" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C82" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="D82" t="s">
         <v>333</v>
@@ -3772,16 +3781,16 @@
         <v>335</v>
       </c>
       <c r="B83" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C83" t="s">
-        <v>436</v>
+        <v>495</v>
       </c>
       <c r="D83" t="s">
-        <v>99</v>
+        <v>336</v>
       </c>
       <c r="E83" t="s">
-        <v>100</v>
+        <v>337</v>
       </c>
       <c r="G83"/>
       <c r="H83"/>
@@ -3790,13 +3799,13 @@
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B84" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C84" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="D84" t="s">
         <v>99</v>
@@ -3811,19 +3820,19 @@
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B85" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C85" t="s">
-        <v>492</v>
+        <v>440</v>
       </c>
       <c r="D85" t="s">
-        <v>338</v>
+        <v>99</v>
       </c>
       <c r="E85" t="s">
-        <v>339</v>
+        <v>100</v>
       </c>
       <c r="G85"/>
       <c r="H85"/>
@@ -3835,16 +3844,16 @@
         <v>340</v>
       </c>
       <c r="B86" t="s">
-        <v>407</v>
+        <v>394</v>
       </c>
       <c r="C86" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="D86" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="E86" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="G86"/>
       <c r="H86"/>
@@ -3853,19 +3862,19 @@
     </row>
     <row r="87">
       <c r="A87" t="s">
+        <v>343</v>
+      </c>
+      <c r="B87" t="s">
+        <v>411</v>
+      </c>
+      <c r="C87" t="s">
+        <v>496</v>
+      </c>
+      <c r="D87" t="s">
         <v>341</v>
       </c>
-      <c r="B87" t="s">
-        <v>408</v>
-      </c>
-      <c r="C87" t="s">
-        <v>493</v>
-      </c>
-      <c r="D87" t="s">
+      <c r="E87" t="s">
         <v>342</v>
-      </c>
-      <c r="E87" t="s">
-        <v>343</v>
       </c>
       <c r="G87"/>
       <c r="H87"/>
@@ -3877,10 +3886,10 @@
         <v>344</v>
       </c>
       <c r="B88" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="C88" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="D88" t="s">
         <v>345</v>
@@ -3898,10 +3907,10 @@
         <v>347</v>
       </c>
       <c r="B89" t="s">
-        <v>395</v>
+        <v>413</v>
       </c>
       <c r="C89" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="D89" t="s">
         <v>348</v>
@@ -3919,10 +3928,10 @@
         <v>350</v>
       </c>
       <c r="B90" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="C90" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="D90" t="s">
         <v>351</v>
@@ -3940,10 +3949,10 @@
         <v>353</v>
       </c>
       <c r="B91" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C91" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="D91" t="s">
         <v>354</v>
@@ -3961,10 +3970,10 @@
         <v>356</v>
       </c>
       <c r="B92" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="C92" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="D92" t="s">
         <v>357</v>
@@ -3982,10 +3991,10 @@
         <v>359</v>
       </c>
       <c r="B93" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C93" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="D93" t="s">
         <v>360</v>
@@ -4003,16 +4012,13 @@
         <v>362</v>
       </c>
       <c r="B94" t="s">
-        <v>410</v>
-      </c>
-      <c r="C94" t="s">
-        <v>500</v>
+        <v>12</v>
       </c>
       <c r="D94" t="s">
-        <v>363</v>
+        <v>230</v>
       </c>
       <c r="E94" t="s">
-        <v>364</v>
+        <v>231</v>
       </c>
       <c r="G94"/>
       <c r="H94"/>
@@ -4021,19 +4027,19 @@
     </row>
     <row r="95">
       <c r="A95" t="s">
+        <v>363</v>
+      </c>
+      <c r="B95" t="s">
+        <v>405</v>
+      </c>
+      <c r="C95" t="s">
+        <v>503</v>
+      </c>
+      <c r="D95" t="s">
+        <v>364</v>
+      </c>
+      <c r="E95" t="s">
         <v>365</v>
-      </c>
-      <c r="B95" t="s">
-        <v>410</v>
-      </c>
-      <c r="C95" t="s">
-        <v>501</v>
-      </c>
-      <c r="D95" t="s">
-        <v>366</v>
-      </c>
-      <c r="E95" t="s">
-        <v>367</v>
       </c>
       <c r="G95"/>
       <c r="H95"/>
@@ -4042,19 +4048,19 @@
     </row>
     <row r="96">
       <c r="A96" t="s">
+        <v>366</v>
+      </c>
+      <c r="B96" t="s">
+        <v>414</v>
+      </c>
+      <c r="C96" t="s">
+        <v>504</v>
+      </c>
+      <c r="D96" t="s">
+        <v>367</v>
+      </c>
+      <c r="E96" t="s">
         <v>368</v>
-      </c>
-      <c r="B96" t="s">
-        <v>401</v>
-      </c>
-      <c r="C96" t="s">
-        <v>502</v>
-      </c>
-      <c r="D96" t="s">
-        <v>369</v>
-      </c>
-      <c r="E96" t="s">
-        <v>370</v>
       </c>
       <c r="G96"/>
       <c r="H96"/>
@@ -4063,19 +4069,19 @@
     </row>
     <row r="97">
       <c r="A97" t="s">
+        <v>369</v>
+      </c>
+      <c r="B97" t="s">
+        <v>414</v>
+      </c>
+      <c r="C97" t="s">
+        <v>505</v>
+      </c>
+      <c r="D97" t="s">
+        <v>370</v>
+      </c>
+      <c r="E97" t="s">
         <v>371</v>
-      </c>
-      <c r="B97" t="s">
-        <v>401</v>
-      </c>
-      <c r="C97" t="s">
-        <v>503</v>
-      </c>
-      <c r="D97" t="s">
-        <v>372</v>
-      </c>
-      <c r="E97" t="s">
-        <v>373</v>
       </c>
       <c r="G97"/>
       <c r="H97"/>
@@ -4084,19 +4090,19 @@
     </row>
     <row r="98">
       <c r="A98" t="s">
+        <v>372</v>
+      </c>
+      <c r="B98" t="s">
+        <v>405</v>
+      </c>
+      <c r="C98" t="s">
+        <v>506</v>
+      </c>
+      <c r="D98" t="s">
+        <v>373</v>
+      </c>
+      <c r="E98" t="s">
         <v>374</v>
-      </c>
-      <c r="B98" t="s">
-        <v>404</v>
-      </c>
-      <c r="C98" t="s">
-        <v>504</v>
-      </c>
-      <c r="D98" t="s">
-        <v>375</v>
-      </c>
-      <c r="E98" t="s">
-        <v>376</v>
       </c>
       <c r="G98"/>
       <c r="H98"/>
@@ -4105,19 +4111,19 @@
     </row>
     <row r="99">
       <c r="A99" t="s">
+        <v>375</v>
+      </c>
+      <c r="B99" t="s">
+        <v>405</v>
+      </c>
+      <c r="C99" t="s">
+        <v>507</v>
+      </c>
+      <c r="D99" t="s">
+        <v>376</v>
+      </c>
+      <c r="E99" t="s">
         <v>377</v>
-      </c>
-      <c r="B99" t="s">
-        <v>411</v>
-      </c>
-      <c r="C99" t="s">
-        <v>505</v>
-      </c>
-      <c r="D99" t="s">
-        <v>378</v>
-      </c>
-      <c r="E99" t="s">
-        <v>379</v>
       </c>
       <c r="G99"/>
       <c r="H99"/>
@@ -4126,19 +4132,19 @@
     </row>
     <row r="100">
       <c r="A100" t="s">
+        <v>378</v>
+      </c>
+      <c r="B100" t="s">
+        <v>408</v>
+      </c>
+      <c r="C100" t="s">
+        <v>508</v>
+      </c>
+      <c r="D100" t="s">
+        <v>379</v>
+      </c>
+      <c r="E100" t="s">
         <v>380</v>
-      </c>
-      <c r="B100" t="s">
-        <v>390</v>
-      </c>
-      <c r="C100" t="s">
-        <v>506</v>
-      </c>
-      <c r="D100" t="s">
-        <v>381</v>
-      </c>
-      <c r="E100" t="s">
-        <v>382</v>
       </c>
       <c r="G100"/>
       <c r="H100"/>
@@ -4147,19 +4153,19 @@
     </row>
     <row r="101">
       <c r="A101" t="s">
+        <v>381</v>
+      </c>
+      <c r="B101" t="s">
+        <v>415</v>
+      </c>
+      <c r="C101" t="s">
+        <v>509</v>
+      </c>
+      <c r="D101" t="s">
+        <v>382</v>
+      </c>
+      <c r="E101" t="s">
         <v>383</v>
-      </c>
-      <c r="B101" t="s">
-        <v>412</v>
-      </c>
-      <c r="C101" t="s">
-        <v>496</v>
-      </c>
-      <c r="D101" t="s">
-        <v>384</v>
-      </c>
-      <c r="E101" t="s">
-        <v>352</v>
       </c>
       <c r="G101"/>
       <c r="H101"/>
@@ -4168,30 +4174,72 @@
     </row>
     <row r="102">
       <c r="A102" t="s">
+        <v>384</v>
+      </c>
+      <c r="B102" t="s">
+        <v>394</v>
+      </c>
+      <c r="C102" t="s">
+        <v>510</v>
+      </c>
+      <c r="D102" t="s">
         <v>385</v>
       </c>
-      <c r="B102" t="s">
-        <v>392</v>
-      </c>
-      <c r="C102" t="s">
-        <v>507</v>
-      </c>
-      <c r="D102" t="s">
+      <c r="E102" t="s">
         <v>386</v>
-      </c>
-      <c r="E102" t="s">
-        <v>387</v>
       </c>
       <c r="G102"/>
       <c r="H102"/>
-      <c r="I102" t="s">
-        <v>551</v>
-      </c>
-      <c r="J102" t="s">
+      <c r="J102"/>
+      <c r="K102"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="s">
+        <v>387</v>
+      </c>
+      <c r="B103" t="s">
+        <v>416</v>
+      </c>
+      <c r="C103" t="s">
+        <v>500</v>
+      </c>
+      <c r="D103" t="s">
         <v>388</v>
       </c>
-      <c r="K102" t="s">
+      <c r="E103" t="s">
+        <v>355</v>
+      </c>
+      <c r="G103"/>
+      <c r="H103"/>
+      <c r="J103"/>
+      <c r="K103"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="s">
         <v>389</v>
+      </c>
+      <c r="B104" t="s">
+        <v>396</v>
+      </c>
+      <c r="C104" t="s">
+        <v>511</v>
+      </c>
+      <c r="D104" t="s">
+        <v>390</v>
+      </c>
+      <c r="E104" t="s">
+        <v>391</v>
+      </c>
+      <c r="G104"/>
+      <c r="H104"/>
+      <c r="I104" t="s">
+        <v>555</v>
+      </c>
+      <c r="J104" t="s">
+        <v>392</v>
+      </c>
+      <c r="K104" t="s">
+        <v>393</v>
       </c>
     </row>
   </sheetData>

--- a/Mod_Korean/Lang/KR/Game/Zone.xlsx
+++ b/Mod_Korean/Lang/KR/Game/Zone.xlsx
@@ -53,7 +53,7 @@
     <t xml:space="preserve">world</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.282 Patch 2</t>
+    <t xml:space="preserve">EA 23.287</t>
   </si>
   <si>
     <t xml:space="preserve">Ylva</t>

--- a/Mod_Korean/Lang/KR/Game/Zone.xlsx
+++ b/Mod_Korean/Lang/KR/Game/Zone.xlsx
@@ -53,7 +53,7 @@
     <t xml:space="preserve">world</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.287</t>
+    <t xml:space="preserve">EA 23.295</t>
   </si>
   <si>
     <t xml:space="preserve">Ylva</t>

--- a/Mod_Korean/Lang/KR/Game/Zone.xlsx
+++ b/Mod_Korean/Lang/KR/Game/Zone.xlsx
@@ -53,7 +53,7 @@
     <t xml:space="preserve">world</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.295</t>
+    <t xml:space="preserve">EA 23.307</t>
   </si>
   <si>
     <t xml:space="preserve">Ylva</t>

--- a/Mod_Korean/Lang/KR/Game/Zone.xlsx
+++ b/Mod_Korean/Lang/KR/Game/Zone.xlsx
@@ -53,7 +53,7 @@
     <t xml:space="preserve">world</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.307</t>
+    <t xml:space="preserve">EA 23.325</t>
   </si>
   <si>
     <t xml:space="preserve">Ylva</t>

--- a/Mod_Korean/Lang/KR/Game/Zone.xlsx
+++ b/Mod_Korean/Lang/KR/Game/Zone.xlsx
@@ -53,7 +53,7 @@
     <t xml:space="preserve">world</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.325</t>
+    <t xml:space="preserve">EA 23.338 Patch 2</t>
   </si>
   <si>
     <t xml:space="preserve">Ylva</t>
